--- a/dev/build/pilot-johnson/johnson-extracted.xlsx
+++ b/dev/build/pilot-johnson/johnson-extracted.xlsx
@@ -1628,6 +1628,11 @@
           <t>DOE FOD impact test matrix</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://github.com/cloudronin/uofa/fod-tire-puncture-regression-model-aircraft-tire-penetration-risk-assessment/predict-aircraft-tire-fod-penetration-depth-to-support-probabilistic-risk-assessment-pra-of-a-ground-hold-decision/dataset/dataset-doe-fod-impact-test-matrix</t>
+        </is>
+      </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Replicated design-of-experiments test matrix (18 planned tests, 15 completed) varying FOD particle velocity and orientation, with penetration depth measured as the response.</t>
@@ -2139,7 +2144,7 @@
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>DOE test data (18-run matrix, 15 completed)</t>
+          <t>https://github.com/cloudronin/uofa/fod-tire-puncture-regression-model-aircraft-tire-penetration-risk-assessment/predict-aircraft-tire-fod-penetration-depth-to-support-probabilistic-risk-assessment-pra-of-a-ground-hold-decision/dataset/dataset-doe-fod-impact-test-matrix</t>
         </is>
       </c>
       <c r="F4" s="14" t="inlineStr">
@@ -2279,7 +2284,43 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Formal DOE development and analysis process</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ProcessAttestation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://github.com/cloudronin/uofa/fod-tire-puncture-regression-model-aircraft-tire-penetration-risk-assessment/predict-aircraft-tire-fod-penetration-depth-to-support-probabilistic-risk-assessment-pra-of-a-ground-hold-decision/evidence/process-attestation-doe</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Standard formal experimental design and data analysis process rigorously followed and documented in standard form. Statistical metrics used to select the best model from a list of candidates. All review comments addressed.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>p.25 M&amp;S Process / Product Management rationale; p.12 4.1.3 a,b</t>
+        </is>
+      </c>
+    </row>
     <row r="9"/>
     <row r="10"/>
     <row r="11"/>
@@ -2977,7 +3018,11 @@
           <t>assessed</t>
         </is>
       </c>
-      <c r="H20" s="10" t="n"/>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/cloudronin/uofa/fod-tire-puncture-regression-model-aircraft-tire-penetration-risk-assessment/predict-aircraft-tire-fod-penetration-depth-to-support-probabilistic-risk-assessment-pra-of-a-ground-hold-decision/evidence/process-attestation-doe</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>req: p.7 Table 3 shading (geometric recovery, TABLE3_RECOVERY.md); ach: p.25</t>

--- a/dev/build/pilot-johnson/johnson-extracted.xlsx
+++ b/dev/build/pilot-johnson/johnson-extracted.xlsx
@@ -2317,7 +2317,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>p.25 M&amp;S Process / Product Management rationale; p.12 4.1.3 a,b</t>
+          <t>p.25 (assessment rationale) + p.24 (M&amp;S 36 review summary) + p.12 §4.1.3(a,b)</t>
         </is>
       </c>
     </row>
